--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486536_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486536_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5385</v>
+        <v>2.5819</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0755</v>
+        <v>3.0264</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.537</v>
+        <v>-0.4445</v>
       </c>
       <c r="G2" t="n">
         <v>-0.736</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6443</v>
+        <v>0.6877</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1512</v>
+        <v>0.1022</v>
       </c>
       <c r="U2" t="n">
-        <v>0.493</v>
+        <v>0.5855</v>
       </c>
       <c r="V2" t="n">
         <v>1.3252</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.86</v>
+        <v>1.2638</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7772</v>
+        <v>3.181</v>
       </c>
       <c r="F3" t="n">
         <v>-1.9172</v>
@@ -688,10 +688,10 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7895</v>
+        <v>-0.3857</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0274</v>
+        <v>-0.6237</v>
       </c>
       <c r="U3" t="n">
         <v>0.2379</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1933</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7061</v>
+        <v>-0.0987</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5129</v>
+        <v>0.1848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5727</v>
+        <v>0.1203</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2052</v>
+        <v>-0.216</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7779</v>
+        <v>0.3363</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4098</v>
+        <v>0.0382</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9395</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3492</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8371</v>
+        <v>0.082</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2657</v>
+        <v>-0.216</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5714</v>
+        <v>0.298</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1627</v>
+        <v>-0.0342</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6813</v>
+        <v>-0.137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8441</v>
+        <v>0.1027</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.0647</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0244</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0987</v>
+        <v>1.7746</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1231</v>
+        <v>-1.6978</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1203</v>
+        <v>0.5727</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.216</v>
+        <v>-2.2052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3363</v>
+        <v>2.7779</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0382</v>
+        <v>2.4098</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.9395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382</v>
+        <v>3.3492</v>
       </c>
       <c r="M5" t="n">
-        <v>0.082</v>
+        <v>-1.8371</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.216</v>
+        <v>-1.2657</v>
       </c>
       <c r="O5" t="n">
-        <v>0.298</v>
+        <v>-0.5714</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0959</v>
+        <v>0.0463</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.137</v>
+        <v>-0.6128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0411</v>
+        <v>0.6591</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.0647</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.996</v>
+        <v>-0.4583</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1792</v>
+        <v>-0.3263</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8167</v>
+        <v>-0.1321</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4748</v>
+        <v>2.1104</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2493</v>
+        <v>1.3016</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2255</v>
+        <v>0.8088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09470000000000001</v>
+        <v>3.847</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0182</v>
+        <v>2.4668</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>1.3802</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3801</v>
+        <v>-1.7366</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2311</v>
+        <v>-1.1652</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.5714</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3408</v>
+        <v>0.3464</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>-0.3881</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0668</v>
+        <v>0.7345</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1781</v>
+        <v>-0.8727</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9535</v>
+        <v>-0.1792</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2245</v>
+        <v>-0.6934</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1104</v>
+        <v>0.4748</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3016</v>
+        <v>0.2493</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8088</v>
+        <v>0.2255</v>
       </c>
       <c r="J7" t="n">
-        <v>3.847</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4668</v>
+        <v>0.0182</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3802</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7366</v>
+        <v>0.3801</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1652</v>
+        <v>0.2311</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5714</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3734</v>
+        <v>-0.2175</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0154</v>
+        <v>-0.274</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6421</v>
+        <v>0.0565</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.604</v>
+        <v>-1.2812</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.2181</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5302</v>
+        <v>-1.4993</v>
       </c>
       <c r="G8" t="n">
         <v>0.5397</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.209</v>
+        <v>0.1139</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8099</v>
+        <v>-0.5179</v>
       </c>
       <c r="U8" t="n">
-        <v>0.601</v>
+        <v>0.6318</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4997</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1852</v>
+        <v>-3.0174</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.48</v>
+        <v>-3.343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2948</v>
+        <v>0.3256</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4233</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.632</v>
+        <v>-0.4642</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2585</v>
+        <v>0.2893</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9388</v>
+        <v>-4.1408</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7181</v>
+        <v>-4.5811</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7794</v>
+        <v>0.4403</v>
       </c>
       <c r="G10" t="n">
         <v>1.0585</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5274</v>
+        <v>0.3254</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7498</v>
+        <v>-0.6128</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2773</v>
+        <v>0.9382</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7395</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4431</v>
+        <v>-4.2821</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3767</v>
+        <v>-2.3082</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0664</v>
+        <v>-1.9739</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3216</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5789</v>
+        <v>-0.4179</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6165</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1061</v>
+        <v>0.1986</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8902</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.729</v>
+        <v>-10.044</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.321299999999999</v>
+        <v>-2.6364</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.4076</v>
+        <v>-7.407500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>4.175000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>9.787699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6850999999999998</v>
+        <v>0.0002000000000000335</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.119</v>
+        <v>-4.4341</v>
       </c>
       <c r="U12" t="n">
-        <v>4.434299999999999</v>
+        <v>4.4341</v>
       </c>
       <c r="V12" t="n">
         <v>-7.693899999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>P. ALI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.299099999999999</v>
+        <v>8.133900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1675</v>
+        <v>4.5049</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1316</v>
+        <v>3.6289</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7405</v>
+        <v>2.0236</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0441</v>
+        <v>-0.4531</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3036</v>
+        <v>2.4766</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4482</v>
+        <v>2.3177</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7979</v>
+        <v>-0.6657</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6502</v>
+        <v>2.9834</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7077</v>
+        <v>-0.2942</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2461</v>
+        <v>0.2127</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9539</v>
+        <v>-0.5068</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7762</v>
+        <v>0.7634</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8292</v>
+        <v>-0.6801</v>
       </c>
       <c r="U13" t="n">
-        <v>1.947</v>
+        <v>1.4435</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2599</v>
+        <v>4.6944</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8902</v>
+        <v>3.9549</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3698</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ALI</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9527</v>
+        <v>6.962</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1697</v>
+        <v>4.3852</v>
       </c>
       <c r="F14" t="n">
-        <v>3.783</v>
+        <v>2.5767</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0236</v>
+        <v>1.7405</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4531</v>
+        <v>2.0441</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4766</v>
+        <v>-0.3036</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3177</v>
+        <v>2.4482</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6657</v>
+        <v>1.7979</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9834</v>
+        <v>0.6502</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2942</v>
+        <v>-0.7077</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2127</v>
+        <v>0.2461</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5068</v>
+        <v>-0.9539</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5822000000000001</v>
+        <v>1.439</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0154</v>
+        <v>0.0469</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5976</v>
+        <v>1.3922</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6944</v>
+        <v>2.2599</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9549</v>
+        <v>1.8902</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7395</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2223</v>
+        <v>1.3713</v>
       </c>
       <c r="E15" t="n">
         <v>1.1172</v>
       </c>
       <c r="F15" t="n">
-        <v>0.105</v>
+        <v>0.2541</v>
       </c>
       <c r="G15" t="n">
         <v>0.5698</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2175</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.149</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3657</v>
+        <v>1.0465</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3963</v>
+        <v>0.6198</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0306</v>
+        <v>0.4267</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2537</v>
@@ -1702,13 +1702,13 @@
         <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0755</v>
+        <v>-0.3948</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2894</v>
+        <v>-1.0659</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2139</v>
+        <v>0.6711</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1537</v>
+        <v>0.3155</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0737</v>
+        <v>0.2973</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0799</v>
+        <v>0.0183</v>
       </c>
       <c r="G17" t="n">
         <v>1.2276</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.1532</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6078</v>
+        <v>0.5462</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3313</v>
+        <v>0.0965</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7075</v>
+        <v>1.0428</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0388</v>
+        <v>-0.9463</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1907</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2929</v>
+        <v>0.1349</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6609</v>
+        <v>-0.3256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3681</v>
+        <v>0.4605</v>
       </c>
       <c r="V18" t="n">
         <v>0.9347</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5804</v>
+        <v>-0.1347</v>
       </c>
       <c r="E19" t="n">
-        <v>1.27</v>
+        <v>1.3818</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8504</v>
+        <v>-1.5165</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6048</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8032</v>
+        <v>-0.3575</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6297</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0618</v>
+        <v>0.2722</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7855</v>
+        <v>-0.5054</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4616</v>
+        <v>-1.238</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6761</v>
+        <v>0.7326</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5324</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2107</v>
+        <v>0.0694</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5744</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5873</v>
+        <v>0.6438</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5158</v>
+        <v>-1.5852</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8904</v>
+        <v>-2.1139</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3745</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9971</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2638</v>
+        <v>0.1944</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>-0.2199</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2602</v>
+        <v>0.4143</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0515</v>
+        <v>-4.2262</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1425</v>
+        <v>-2.5895</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.909</v>
+        <v>-1.6367</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1577</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3288</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0769</v>
+        <v>-0.5239</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2519</v>
+        <v>0.0204</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.729</v>
+        <v>11.4742</v>
       </c>
       <c r="E23" t="n">
-        <v>7.407400000000001</v>
+        <v>7.4076</v>
       </c>
       <c r="F23" t="n">
-        <v>3.321300000000001</v>
+        <v>4.0665</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1749</v>
@@ -2248,13 +2248,13 @@
         <v>16.313</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6848999999999994</v>
+        <v>1.43</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.434100000000001</v>
+        <v>-4.434</v>
       </c>
       <c r="U23" t="n">
-        <v>5.1192</v>
+        <v>5.8642</v>
       </c>
       <c r="V23" t="n">
         <v>7.693700000000001</v>
